--- a/output/2026-09-13_18_Croazia_Bjelovarsko-bilogorska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-13_18_Croazia_Bjelovarsko-bilogorska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore ufficiale SKF (cuscinetti, tenute, utensili, grassi, strumenti di misura), distributore Gates e rappresentante Optibelt (cinghie industria/agricoltura). Fondata 1991, 16 dipendenti, sede Pakračka ulica 3, Bjelovar.</t>
+          <t>Distributore ufficiale SKF (cuscinetti, tenute, utensili, grassi, strumenti di misura), distributore Gates e rappresentante Optibelt (cinghie industria/agricoltura). Fondata 1991, 16 dipendenti, sede Pakračka ulica 3, Bjelovar. [DUPLICATO — vedi anche: 2026-09-13_17_Croazia_Bjelovarsko-bilogorska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rivenditore di utensili professionali/hobbistici, attrezzature da officina, saldatrici, compressori, dischi da taglio/molatura, ferramenta e viteria. Punto vendita anche a Bulinac 57, 43273 Bulinac.</t>
+          <t>Rivenditore di utensili professionali/hobbistici, attrezzature da officina, saldatrici, compressori, dischi da taglio/molatura, ferramenta e viteria. Punto vendita anche a Bulinac 57, 43273 Bulinac. [DUPLICATO — vedi anche: 2026-09-13_17_Croazia_Bjelovarsko-bilogorska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ferramenta industriale, viteria e bulloneria, metallurgia ferrosa e non ferrosa, utensili elettrici, vendita ingrosso/dettaglio. Fondata 1995, 17 dipendenti, due sedi (Bjelovar e Garešnica).</t>
+          <t>Ferramenta industriale, viteria e bulloneria, metallurgia ferrosa e non ferrosa, utensili elettrici, vendita ingrosso/dettaglio. Fondata 1995, 17 dipendenti, due sedi (Bjelovar e Garešnica). [DUPLICATO — vedi anche: 2026-09-13_17_Croazia_Bjelovarsko-bilogorska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-13_18_Croazia_Bjelovarsko-bilogorska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-13_18_Croazia_Bjelovarsko-bilogorska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
